--- a/data/processed/harmonization/Nitrogen__Nitrate_nitrogen/10.15485_2382715/10.15485_2382715_soil_Nitrogen__Nitrate_nitrogen.xlsx
+++ b/data/processed/harmonization/Nitrogen__Nitrate_nitrogen/10.15485_2382715/10.15485_2382715_soil_Nitrogen__Nitrate_nitrogen.xlsx
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2021</t>
+          <t>D11:2021:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -575,12 +575,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2021</t>
+          <t>D11:2021:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -626,12 +626,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2021</t>
+          <t>D11:2021:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2021</t>
+          <t>D12:2021:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2021</t>
+          <t>D12:2021:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -779,12 +779,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2021</t>
+          <t>D12:2021:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2021</t>
+          <t>D13:2021:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -881,12 +881,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2021</t>
+          <t>D13:2021:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -932,12 +932,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2021</t>
+          <t>D13:2021:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2021</t>
+          <t>D14:2021:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2021</t>
+          <t>D14:2021:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2021</t>
+          <t>D14:2021:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2021</t>
+          <t>D15:2021:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2021</t>
+          <t>D15:2021:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2021</t>
+          <t>D15:2021:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2021</t>
+          <t>D16:2021:16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2021</t>
+          <t>D16:2021:17</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2021</t>
+          <t>D16:2021:18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2021</t>
+          <t>E1:2021:19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2021</t>
+          <t>E1:2021:20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2021</t>
+          <t>E1:2021:21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2021</t>
+          <t>E2:2021:22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2021</t>
+          <t>E2:2021:23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2021</t>
+          <t>E2:2021:24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2021</t>
+          <t>E3:2021:25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2021</t>
+          <t>E3:2021:26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2021</t>
+          <t>E3:2021:27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2021</t>
+          <t>E4:2021:28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2021</t>
+          <t>E4:2021:29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2021</t>
+          <t>E4:2021:30</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2021</t>
+          <t>E5:2021:31</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2021</t>
+          <t>E5:2021:32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2021</t>
+          <t>E5:2021:33</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2021</t>
+          <t>E6:2021:34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2021</t>
+          <t>E6:2021:35</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2021</t>
+          <t>E6:2021:36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2021</t>
+          <t>D1:2021:38</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2021</t>
+          <t>D1:2021:39</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2021</t>
+          <t>D2:2021:40</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2021</t>
+          <t>D2:2021:41</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2021</t>
+          <t>D2:2021:42</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2021</t>
+          <t>D3:2021:43</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2021</t>
+          <t>D3:2021:44</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2021</t>
+          <t>D3:2021:45</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2021</t>
+          <t>D4:2021:46</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2021</t>
+          <t>D4:2021:47</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2021</t>
+          <t>D4:2021:48</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2021</t>
+          <t>D5:2021:49</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2021</t>
+          <t>D5:2021:50</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2021</t>
+          <t>D5:2021:51</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2021</t>
+          <t>D6:2021:52</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2021</t>
+          <t>D6:2021:53</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2021</t>
+          <t>D6:2021:54</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2021</t>
+          <t>E7:2021:55</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2021</t>
+          <t>E7:2021:56</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2021</t>
+          <t>E7:2021:57</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2021</t>
+          <t>E8:2021:58</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2021</t>
+          <t>E8:2021:59</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2021</t>
+          <t>E8:2021:60</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2021</t>
+          <t>E9:2021:61</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2021</t>
+          <t>E9:2021:62</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2021</t>
+          <t>E9:2021:63</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2021</t>
+          <t>E10:2021:64</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2021</t>
+          <t>E10:2021:65</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2021</t>
+          <t>E10:2021:66</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2021</t>
+          <t>E11:2021:67</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2021</t>
+          <t>E11:2021:68</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2021</t>
+          <t>E11:2021:69</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2021</t>
+          <t>E12:2021:70</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2021</t>
+          <t>E12:2021:71</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2021</t>
+          <t>E12:2021:72</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2022</t>
+          <t>D11:2022:1</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2022</t>
+          <t>D11:2022:2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2022</t>
+          <t>D11:2022:3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2022</t>
+          <t>D12:2022:4</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2022</t>
+          <t>D12:2022:5</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2022</t>
+          <t>D12:2022:6</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2022</t>
+          <t>D13:2022:7</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4502,12 +4502,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2022</t>
+          <t>D13:2022:8</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4553,12 +4553,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2022</t>
+          <t>D13:2022:9</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2022</t>
+          <t>D14:2022:10</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2022</t>
+          <t>D14:2022:11</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2022</t>
+          <t>D14:2022:12</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2022</t>
+          <t>D15:2022:13</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2022</t>
+          <t>D15:2022:14</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2022</t>
+          <t>D15:2022:15</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2022</t>
+          <t>D16:2022:16</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2022</t>
+          <t>D16:2022:17</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5012,12 +5012,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2022</t>
+          <t>D16:2022:18</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2022</t>
+          <t>E1:2022:19</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2022</t>
+          <t>E1:2022:20</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2022</t>
+          <t>E1:2022:21</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2022</t>
+          <t>E2:2022:22</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2022</t>
+          <t>E2:2022:23</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2022</t>
+          <t>E2:2022:24</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2022</t>
+          <t>E3:2022:25</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5420,12 +5420,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2022</t>
+          <t>E3:2022:26</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5471,12 +5471,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2022</t>
+          <t>E3:2022:27</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5522,12 +5522,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2022</t>
+          <t>E4:2022:28</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5573,12 +5573,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2022</t>
+          <t>E4:2022:29</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2022</t>
+          <t>E4:2022:30</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5675,12 +5675,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2022</t>
+          <t>E5:2022:31</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2022</t>
+          <t>E5:2022:32</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -5777,12 +5777,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2022</t>
+          <t>E5:2022:33</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2022</t>
+          <t>E6:2022:34</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2022</t>
+          <t>E6:2022:35</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2022</t>
+          <t>E6:2022:36</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>D1:37:2022</t>
+          <t>D1:2022:37</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6032,12 +6032,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2022</t>
+          <t>D1:2022:38</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -6083,12 +6083,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2022</t>
+          <t>D1:2022:39</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2022</t>
+          <t>D2:2022:40</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2022</t>
+          <t>D2:2022:41</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6236,12 +6236,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2022</t>
+          <t>D2:2022:42</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6287,12 +6287,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2022</t>
+          <t>D3:2022:43</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2022</t>
+          <t>D3:2022:44</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2022</t>
+          <t>D3:2022:45</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2022</t>
+          <t>D4:2022:46</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2022</t>
+          <t>D4:2022:47</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2022</t>
+          <t>D4:2022:48</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6593,12 +6593,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2022</t>
+          <t>D5:2022:49</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2022</t>
+          <t>D5:2022:50</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -6695,12 +6695,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2022</t>
+          <t>D5:2022:51</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2022</t>
+          <t>D6:2022:52</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2022</t>
+          <t>D6:2022:53</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2022</t>
+          <t>D6:2022:54</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2022</t>
+          <t>E7:2022:55</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2022</t>
+          <t>E7:2022:56</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -7001,12 +7001,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2022</t>
+          <t>E7:2022:57</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -7052,12 +7052,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2022</t>
+          <t>E8:2022:58</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2022</t>
+          <t>E8:2022:59</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2022</t>
+          <t>E8:2022:60</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -7205,12 +7205,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2022</t>
+          <t>E9:2022:61</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -7256,12 +7256,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2022</t>
+          <t>E9:2022:62</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -7307,12 +7307,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2022</t>
+          <t>E9:2022:63</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -7358,12 +7358,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2022</t>
+          <t>E10:2022:64</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2022</t>
+          <t>E10:2022:65</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2022</t>
+          <t>E10:2022:66</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -7511,12 +7511,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2022</t>
+          <t>E11:2022:69</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2022</t>
+          <t>E12:2022:70</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2022</t>
+          <t>E12:2022:71</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2022</t>
+          <t>E12:2022:72</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2021</t>
+          <t>D11:2021:1</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2021</t>
+          <t>D11:2021:2</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -7817,12 +7817,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2021</t>
+          <t>D11:2021:3</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2021</t>
+          <t>D12:2021:4</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2021</t>
+          <t>D12:2021:5</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -7970,12 +7970,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2021</t>
+          <t>D12:2021:6</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2021</t>
+          <t>D13:2021:7</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -8072,12 +8072,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2021</t>
+          <t>D13:2021:8</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2021</t>
+          <t>D13:2021:9</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2021</t>
+          <t>D14:2021:10</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2021</t>
+          <t>D14:2021:11</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -8276,12 +8276,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2021</t>
+          <t>D14:2021:12</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -8327,12 +8327,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2021</t>
+          <t>D15:2021:13</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2021</t>
+          <t>D15:2021:14</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2021</t>
+          <t>D15:2021:15</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2021</t>
+          <t>D16:2021:16</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2021</t>
+          <t>D16:2021:17</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2021</t>
+          <t>D16:2021:18</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -8633,12 +8633,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2021</t>
+          <t>E1:2021:19</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2021</t>
+          <t>E1:2021:20</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2021</t>
+          <t>E1:2021:21</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -8786,12 +8786,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2021</t>
+          <t>E2:2021:22</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -8837,12 +8837,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2021</t>
+          <t>E2:2021:23</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -8888,12 +8888,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2021</t>
+          <t>E2:2021:24</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2021</t>
+          <t>E3:2021:25</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -8990,12 +8990,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2021</t>
+          <t>E3:2021:26</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -9041,12 +9041,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2021</t>
+          <t>E3:2021:27</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2021</t>
+          <t>E4:2021:28</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -9143,12 +9143,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2021</t>
+          <t>E4:2021:29</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2021</t>
+          <t>E4:2021:30</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2021</t>
+          <t>E5:2021:31</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2021</t>
+          <t>E5:2021:32</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2021</t>
+          <t>E5:2021:33</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2021</t>
+          <t>E6:2021:34</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -9449,12 +9449,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2021</t>
+          <t>E6:2021:35</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -9500,12 +9500,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2021</t>
+          <t>E6:2021:36</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -9551,12 +9551,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2021</t>
+          <t>D1:2021:38</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2021</t>
+          <t>D1:2021:39</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -9653,12 +9653,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2021</t>
+          <t>D2:2021:40</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2021</t>
+          <t>D2:2021:41</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2021</t>
+          <t>D2:2021:42</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2021</t>
+          <t>D3:2021:43</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2021</t>
+          <t>D3:2021:44</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -9908,12 +9908,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2021</t>
+          <t>D3:2021:45</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2021</t>
+          <t>D4:2021:46</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2021</t>
+          <t>D4:2021:47</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2021</t>
+          <t>D4:2021:48</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -10112,12 +10112,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2021</t>
+          <t>D5:2021:49</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -10163,12 +10163,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2021</t>
+          <t>D5:2021:50</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2021</t>
+          <t>D5:2021:51</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -10265,12 +10265,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2021</t>
+          <t>D6:2021:52</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -10316,12 +10316,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2021</t>
+          <t>D6:2021:53</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -10367,12 +10367,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2021</t>
+          <t>D6:2021:54</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2021</t>
+          <t>E7:2021:55</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2021</t>
+          <t>E7:2021:56</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -10520,12 +10520,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2021</t>
+          <t>E7:2021:57</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
@@ -10571,12 +10571,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2021</t>
+          <t>E8:2021:58</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2021</t>
+          <t>E8:2021:59</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2021</t>
+          <t>E8:2021:60</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr"/>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2021</t>
+          <t>E9:2021:61</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
@@ -10775,12 +10775,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2021</t>
+          <t>E9:2021:62</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2021</t>
+          <t>E9:2021:63</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2021</t>
+          <t>E10:2021:64</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
@@ -10928,12 +10928,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2021</t>
+          <t>E10:2021:65</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -10979,12 +10979,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2021</t>
+          <t>E10:2021:66</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
@@ -11030,12 +11030,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2021</t>
+          <t>E11:2021:67</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -11081,12 +11081,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2021</t>
+          <t>E11:2021:68</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -11132,12 +11132,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2021</t>
+          <t>E11:2021:69</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2021</t>
+          <t>E12:2021:70</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2021</t>
+          <t>E12:2021:71</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2021</t>
+          <t>E12:2021:72</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
@@ -11336,12 +11336,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2022</t>
+          <t>D11:2022:1</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -11387,12 +11387,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2022</t>
+          <t>D11:2022:2</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr"/>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2022</t>
+          <t>D11:2022:3</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
@@ -11489,12 +11489,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2022</t>
+          <t>D12:2022:4</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr"/>
@@ -11540,12 +11540,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2022</t>
+          <t>D12:2022:5</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -11591,12 +11591,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2022</t>
+          <t>D12:2022:6</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
@@ -11642,12 +11642,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2022</t>
+          <t>D13:2022:7</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2022</t>
+          <t>D13:2022:8</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
@@ -11744,12 +11744,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2022</t>
+          <t>D13:2022:9</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2022</t>
+          <t>D14:2022:10</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
@@ -11846,12 +11846,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2022</t>
+          <t>D14:2022:11</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2022</t>
+          <t>D14:2022:12</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
@@ -11948,12 +11948,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2022</t>
+          <t>D15:2022:13</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
@@ -11999,12 +11999,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2022</t>
+          <t>D15:2022:14</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
@@ -12050,12 +12050,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2022</t>
+          <t>D15:2022:15</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
@@ -12101,12 +12101,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2022</t>
+          <t>D16:2022:16</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
@@ -12152,12 +12152,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2022</t>
+          <t>D16:2022:17</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -12203,12 +12203,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2022</t>
+          <t>D16:2022:18</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2022</t>
+          <t>E1:2022:19</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
@@ -12305,12 +12305,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2022</t>
+          <t>E1:2022:20</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
@@ -12356,12 +12356,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2022</t>
+          <t>E1:2022:21</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
@@ -12407,12 +12407,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2022</t>
+          <t>E2:2022:22</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr"/>
@@ -12458,12 +12458,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2022</t>
+          <t>E2:2022:23</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
@@ -12509,12 +12509,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2022</t>
+          <t>E2:2022:24</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr"/>
@@ -12560,12 +12560,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2022</t>
+          <t>E3:2022:25</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
@@ -12611,12 +12611,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2022</t>
+          <t>E3:2022:26</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr"/>
@@ -12662,12 +12662,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2022</t>
+          <t>E3:2022:27</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr"/>
@@ -12713,12 +12713,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2022</t>
+          <t>E4:2022:28</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr"/>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2022</t>
+          <t>E4:2022:29</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
@@ -12815,12 +12815,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2022</t>
+          <t>E4:2022:30</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr"/>
@@ -12866,12 +12866,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2022</t>
+          <t>E5:2022:31</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
@@ -12917,12 +12917,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2022</t>
+          <t>E5:2022:32</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr"/>
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2022</t>
+          <t>E5:2022:33</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
@@ -13019,12 +13019,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2022</t>
+          <t>E6:2022:34</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr"/>
@@ -13070,12 +13070,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2022</t>
+          <t>E6:2022:35</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2022</t>
+          <t>E6:2022:36</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
@@ -13172,12 +13172,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>D1:37:2022</t>
+          <t>D1:2022:37</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2022</t>
+          <t>D1:2022:38</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
@@ -13274,12 +13274,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2022</t>
+          <t>D1:2022:39</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2022</t>
+          <t>D2:2022:40</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr"/>
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2022</t>
+          <t>D2:2022:41</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr"/>
@@ -13427,12 +13427,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2022</t>
+          <t>D2:2022:42</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr"/>
@@ -13478,12 +13478,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2022</t>
+          <t>D3:2022:43</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2022</t>
+          <t>D3:2022:44</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2022</t>
+          <t>D3:2022:45</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
@@ -13631,12 +13631,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2022</t>
+          <t>D4:2022:46</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
@@ -13682,12 +13682,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2022</t>
+          <t>D4:2022:47</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
@@ -13733,12 +13733,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2022</t>
+          <t>D4:2022:48</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr"/>
@@ -13784,12 +13784,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2022</t>
+          <t>D5:2022:49</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2022</t>
+          <t>D5:2022:50</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr"/>
@@ -13886,12 +13886,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2022</t>
+          <t>D5:2022:51</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr"/>
@@ -13937,12 +13937,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2022</t>
+          <t>D6:2022:52</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
@@ -13988,12 +13988,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2022</t>
+          <t>D6:2022:53</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr"/>
@@ -14039,12 +14039,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2022</t>
+          <t>D6:2022:54</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr"/>
@@ -14090,12 +14090,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2022</t>
+          <t>E7:2022:55</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr"/>
@@ -14141,12 +14141,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2022</t>
+          <t>E7:2022:56</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr"/>
@@ -14192,12 +14192,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2022</t>
+          <t>E7:2022:57</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
@@ -14243,12 +14243,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2022</t>
+          <t>E8:2022:58</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
@@ -14294,12 +14294,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2022</t>
+          <t>E8:2022:59</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr"/>
@@ -14345,12 +14345,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2022</t>
+          <t>E8:2022:60</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr"/>
@@ -14396,12 +14396,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2022</t>
+          <t>E9:2022:61</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr"/>
@@ -14447,12 +14447,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2022</t>
+          <t>E9:2022:62</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
@@ -14498,12 +14498,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2022</t>
+          <t>E9:2022:63</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr"/>
@@ -14549,12 +14549,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2022</t>
+          <t>E10:2022:64</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
@@ -14600,12 +14600,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2022</t>
+          <t>E10:2022:65</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr"/>
@@ -14651,12 +14651,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2022</t>
+          <t>E10:2022:66</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
@@ -14702,12 +14702,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2022</t>
+          <t>E11:2022:67</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
@@ -14753,12 +14753,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2022</t>
+          <t>E11:2022:68</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
@@ -14804,12 +14804,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2022</t>
+          <t>E11:2022:69</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
@@ -14855,12 +14855,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2022</t>
+          <t>E12:2022:70</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr"/>
@@ -14906,12 +14906,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2022</t>
+          <t>E12:2022:71</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr"/>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2022</t>
+          <t>E12:2022:72</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr"/>
